--- a/data/trans_orig/P78_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P78_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona sustentadora principal trabaja actualmente en 2023</t>
+          <t>Población según si la persona sustentadora principal trabaja actualmente en 2023 (tasa de respuesta: 99,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>345107</t>
+          <t>343501</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>365163</t>
+          <t>365295</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>322741</t>
+          <t>322990</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>336867</t>
+          <t>337550</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>673882</t>
+          <t>674504</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>699399</t>
+          <t>699634</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22843</t>
+          <t>24449</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>8178</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22987</t>
+          <t>22738</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14279</t>
+          <t>14044</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39796</t>
+          <t>39174</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>302973</t>
+          <t>303079</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>313499</t>
+          <t>313147</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>274222</t>
+          <t>274904</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>287745</t>
+          <t>287897</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>582364</t>
+          <t>582758</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>598666</t>
+          <t>598492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12797</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21886</t>
+          <t>21204</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13212</t>
+          <t>13386</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29514</t>
+          <t>29120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>483055</t>
+          <t>483087</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>497404</t>
+          <t>497566</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,97%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79542</t>
+          <t>80255</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94602</t>
+          <t>93930</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>557228</t>
+          <t>557189</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>599399</t>
+          <t>601447</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14511</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16282</t>
+          <t>16954</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31342</t>
+          <t>30629</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9051</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51222</t>
+          <t>51261</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>567874</t>
+          <t>563868</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>602822</t>
+          <t>601899</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>222228</t>
+          <t>208542</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>685368</t>
+          <t>684779</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>648562</t>
+          <t>583434</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1284049</t>
+          <t>1282997</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,68%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18768</t>
+          <t>19691</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53716</t>
+          <t>57722</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77324</t>
+          <t>77913</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>540464</t>
+          <t>554150</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>100232</t>
+          <t>101284</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>735719</t>
+          <t>800847</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>57,85%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>239603</t>
+          <t>239785</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>257350</t>
+          <t>257791</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>430918</t>
+          <t>433834</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>494086</t>
+          <t>495296</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>681911</t>
+          <t>682994</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>738140</t>
+          <t>738428</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,16%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9814</t>
+          <t>9373</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27561</t>
+          <t>27379</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>66965</t>
+          <t>65755</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130133</t>
+          <t>127217</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>90075</t>
+          <t>89787</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>146304</t>
+          <t>145221</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>179538</t>
+          <t>176145</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>214022</t>
+          <t>213043</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>319780</t>
+          <t>320256</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>371732</t>
+          <t>373078</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>510104</t>
+          <t>506791</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>580145</t>
+          <t>579857</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,55%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22734</t>
+          <t>23713</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57218</t>
+          <t>60611</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>365230</t>
+          <t>363884</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>417182</t>
+          <t>416706</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>393572</t>
+          <t>393860</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>463613</t>
+          <t>466926</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,95%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2161362</t>
+          <t>2161550</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2233516</t>
+          <t>2232473</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1556735</t>
+          <t>1574205</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2177715</t>
+          <t>2181692</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3528551</t>
+          <t>3509608</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4410709</t>
+          <t>4407520</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,08%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>73279</t>
+          <t>74322</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>145433</t>
+          <t>145245</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>635708</t>
+          <t>631731</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1256688</t>
+          <t>1239218</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>709510</t>
+          <t>712699</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1591668</t>
+          <t>1610611</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,46%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P78_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P78_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>359378</t>
+          <t>391444</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>343501</t>
+          <t>378551</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>365295</t>
+          <t>396968</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>331618</t>
+          <t>356732</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>322990</t>
+          <t>348462</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>337550</t>
+          <t>362837</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>690996</t>
+          <t>748177</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>674504</t>
+          <t>735558</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>699634</t>
+          <t>756183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24449</t>
+          <t>21018</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14110</t>
+          <t>14692</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22738</t>
+          <t>22962</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>22682</t>
+          <t>22817</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14044</t>
+          <t>14811</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39174</t>
+          <t>35436</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>367950</t>
+          <t>399569</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>367950</t>
+          <t>399569</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>367950</t>
+          <t>399569</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>345728</t>
+          <t>371424</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>345728</t>
+          <t>371424</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>345728</t>
+          <t>371424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713678</t>
+          <t>770994</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713678</t>
+          <t>770994</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713678</t>
+          <t>770994</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>309596</t>
+          <t>328388</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>303079</t>
+          <t>321878</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>313147</t>
+          <t>332202</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>282160</t>
+          <t>306792</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>274904</t>
+          <t>298253</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>287897</t>
+          <t>312472</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>591756</t>
+          <t>635179</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>582758</t>
+          <t>624901</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>598492</t>
+          <t>641789</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6174</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12691</t>
+          <t>13446</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>14215</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>22754</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>21152</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13386</t>
+          <t>14542</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29120</t>
+          <t>31430</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>315770</t>
+          <t>335324</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>315770</t>
+          <t>335324</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>315770</t>
+          <t>335324</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>296108</t>
+          <t>321007</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>296108</t>
+          <t>321007</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>296108</t>
+          <t>321007</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>611878</t>
+          <t>656331</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>611878</t>
+          <t>656331</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>611878</t>
+          <t>656331</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>492454</t>
+          <t>276482</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>483087</t>
+          <t>267029</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>497566</t>
+          <t>281709</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>88141</t>
+          <t>100167</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80255</t>
+          <t>89851</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93930</t>
+          <t>107293</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>580595</t>
+          <t>376649</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>557189</t>
+          <t>364101</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>601447</t>
+          <t>386576</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14479</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22743</t>
+          <t>25084</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16954</t>
+          <t>17958</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30629</t>
+          <t>35400</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>27855</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>23150</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51261</t>
+          <t>45625</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>497566</t>
+          <t>284475</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>497566</t>
+          <t>284475</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>497566</t>
+          <t>284475</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>110884</t>
+          <t>125251</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>110884</t>
+          <t>125251</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>110884</t>
+          <t>125251</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>608450</t>
+          <t>409726</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>608450</t>
+          <t>409726</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>608450</t>
+          <t>409726</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>589299</t>
+          <t>654635</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>563868</t>
+          <t>632814</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>601899</t>
+          <t>667436</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>496719</t>
+          <t>557493</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>208542</t>
+          <t>543717</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>684779</t>
+          <t>569662</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1086017</t>
+          <t>1212128</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>583434</t>
+          <t>1188700</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1282997</t>
+          <t>1229512</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>32291</t>
+          <t>30962</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19691</t>
+          <t>18161</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57722</t>
+          <t>52783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>265973</t>
+          <t>66224</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77913</t>
+          <t>54055</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>554150</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>298264</t>
+          <t>97186</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>101284</t>
+          <t>79802</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>800847</t>
+          <t>120614</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>621590</t>
+          <t>685597</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>621590</t>
+          <t>685597</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>621590</t>
+          <t>685597</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>762692</t>
+          <t>623717</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>762692</t>
+          <t>623717</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>762692</t>
+          <t>623717</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1384281</t>
+          <t>1309314</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1384281</t>
+          <t>1309314</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1384281</t>
+          <t>1309314</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>250804</t>
+          <t>323692</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>239785</t>
+          <t>312514</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>257791</t>
+          <t>330661</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>457231</t>
+          <t>408747</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>433834</t>
+          <t>389426</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>495296</t>
+          <t>422523</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>708035</t>
+          <t>732439</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>682994</t>
+          <t>710970</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>738428</t>
+          <t>748388</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16360</t>
+          <t>16758</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9373</t>
+          <t>9789</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27379</t>
+          <t>27936</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>103820</t>
+          <t>111766</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65755</t>
+          <t>97990</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>127217</t>
+          <t>131087</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>120180</t>
+          <t>128524</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>89787</t>
+          <t>112575</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>145221</t>
+          <t>149993</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>267164</t>
+          <t>340450</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>267164</t>
+          <t>340450</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>267164</t>
+          <t>340450</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>561051</t>
+          <t>520513</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>561051</t>
+          <t>520513</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>561051</t>
+          <t>520513</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>828215</t>
+          <t>860963</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>828215</t>
+          <t>860963</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>828215</t>
+          <t>860963</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>198894</t>
+          <t>196402</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>176145</t>
+          <t>179017</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>213043</t>
+          <t>209070</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>345914</t>
+          <t>402588</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>320256</t>
+          <t>375218</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>373078</t>
+          <t>431132</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>544807</t>
+          <t>598990</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>506791</t>
+          <t>566040</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>579857</t>
+          <t>634570</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>60,42%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>37862</t>
+          <t>35326</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23713</t>
+          <t>22658</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60611</t>
+          <t>52711</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>391048</t>
+          <t>416017</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>363884</t>
+          <t>387473</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>416706</t>
+          <t>443387</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>428910</t>
+          <t>451344</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>393860</t>
+          <t>415764</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>466926</t>
+          <t>484294</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>46,11%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>236756</t>
+          <t>231728</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>236756</t>
+          <t>231728</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>236756</t>
+          <t>231728</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>736962</t>
+          <t>818605</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>736962</t>
+          <t>818605</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>736962</t>
+          <t>818605</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>973717</t>
+          <t>1050334</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>973717</t>
+          <t>1050334</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>973717</t>
+          <t>1050334</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2200424</t>
+          <t>2171043</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2161550</t>
+          <t>2143782</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2232473</t>
+          <t>2196092</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2001782</t>
+          <t>2132519</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1574205</t>
+          <t>2093151</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2181692</t>
+          <t>2169035</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4202207</t>
+          <t>4303563</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3509608</t>
+          <t>4252667</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4407520</t>
+          <t>4344998</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,91%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>106371</t>
+          <t>106100</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>74322</t>
+          <t>81051</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>145245</t>
+          <t>133361</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>811641</t>
+          <t>647999</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>631731</t>
+          <t>611483</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1239218</t>
+          <t>687367</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>918012</t>
+          <t>754099</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>712699</t>
+          <t>712664</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1610611</t>
+          <t>804995</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2306795</t>
+          <t>2277143</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2306795</t>
+          <t>2277143</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2306795</t>
+          <t>2277143</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2813423</t>
+          <t>2780518</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2813423</t>
+          <t>2780518</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2813423</t>
+          <t>2780518</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>5120219</t>
+          <t>5057662</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5120219</t>
+          <t>5057662</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5120219</t>
+          <t>5057662</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
